--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/97.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/97.xlsx
@@ -426,13 +426,13 @@
         <v>-24.03227956690473</v>
       </c>
       <c r="E2">
-        <v>-20.34752774084598</v>
+        <v>-15.99529037612033</v>
       </c>
       <c r="F2">
-        <v>-4.603709145656554</v>
+        <v>-3.140676460058567</v>
       </c>
       <c r="G2">
-        <v>-14.87259553371858</v>
+        <v>-15.47439174255463</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-23.74811473552072</v>
       </c>
       <c r="E3">
-        <v>-20.04998752832394</v>
+        <v>-17.06713454198679</v>
       </c>
       <c r="F3">
-        <v>-4.249792486280076</v>
+        <v>-2.787805200344423</v>
       </c>
       <c r="G3">
-        <v>-14.45992035769049</v>
+        <v>-15.17398641617818</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-23.46128234976293</v>
       </c>
       <c r="E4">
-        <v>-20.47112730987288</v>
+        <v>-17.08484383507585</v>
       </c>
       <c r="F4">
-        <v>-4.339167530470323</v>
+        <v>-2.93318202280093</v>
       </c>
       <c r="G4">
-        <v>-14.28803023918389</v>
+        <v>-14.65837610778397</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-23.22513371239759</v>
       </c>
       <c r="E5">
-        <v>-21.4207715389289</v>
+        <v>-17.68242034012616</v>
       </c>
       <c r="F5">
-        <v>-3.229512237069592</v>
+        <v>-2.772836601375836</v>
       </c>
       <c r="G5">
-        <v>-13.88495738176191</v>
+        <v>-14.50901410435408</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-23.01218474612434</v>
       </c>
       <c r="E6">
-        <v>-21.02264885454216</v>
+        <v>-17.79128016216124</v>
       </c>
       <c r="F6">
-        <v>-4.079837174615104</v>
+        <v>-2.742541548720652</v>
       </c>
       <c r="G6">
-        <v>-14.63352443002116</v>
+        <v>-13.92576723583789</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-22.82085187285293</v>
       </c>
       <c r="E7">
-        <v>-23.07477548940789</v>
+        <v>-19.34411188476741</v>
       </c>
       <c r="F7">
-        <v>-4.826950847241409</v>
+        <v>-2.76587831519232</v>
       </c>
       <c r="G7">
-        <v>-13.82783690085294</v>
+        <v>-14.29927341076552</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-22.6358580369106</v>
       </c>
       <c r="E8">
-        <v>-21.52311912560665</v>
+        <v>-19.73134069584912</v>
       </c>
       <c r="F8">
-        <v>-3.878079181621854</v>
+        <v>-2.341215766147153</v>
       </c>
       <c r="G8">
-        <v>-13.67722043464702</v>
+        <v>-13.63483891232718</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-22.42471087402337</v>
       </c>
       <c r="E9">
-        <v>-20.74016403307262</v>
+        <v>-19.70370522769371</v>
       </c>
       <c r="F9">
-        <v>-3.935964667362081</v>
+        <v>-2.434296926097525</v>
       </c>
       <c r="G9">
-        <v>-13.24311496164277</v>
+        <v>-13.31131022110724</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-22.18794089536096</v>
       </c>
       <c r="E10">
-        <v>-22.48507762624079</v>
+        <v>-20.55474806668698</v>
       </c>
       <c r="F10">
-        <v>-4.220482362466821</v>
+        <v>-2.452231908735537</v>
       </c>
       <c r="G10">
-        <v>-13.29077540952584</v>
+        <v>-12.9227100263261</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-21.89492149697252</v>
       </c>
       <c r="E11">
-        <v>-22.36611719426373</v>
+        <v>-21.02519061987296</v>
       </c>
       <c r="F11">
-        <v>-3.504666067053087</v>
+        <v>-1.98717899349727</v>
       </c>
       <c r="G11">
-        <v>-12.59513598636223</v>
+        <v>-12.71763212257726</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-21.56650659020276</v>
       </c>
       <c r="E12">
-        <v>-25.4920939960658</v>
+        <v>-21.24560154488161</v>
       </c>
       <c r="F12">
-        <v>-2.708198264567987</v>
+        <v>-2.199797711508625</v>
       </c>
       <c r="G12">
-        <v>-11.82047585128709</v>
+        <v>-11.98059281706007</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-21.19035232489888</v>
       </c>
       <c r="E13">
-        <v>-26.41537779284313</v>
+        <v>-22.64728960095462</v>
       </c>
       <c r="F13">
-        <v>-3.19494198024856</v>
+        <v>-2.058892416292429</v>
       </c>
       <c r="G13">
-        <v>-12.31155299275862</v>
+        <v>-11.43947292326609</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-20.7931152275174</v>
       </c>
       <c r="E14">
-        <v>-26.20892996430856</v>
+        <v>-23.37810112530542</v>
       </c>
       <c r="F14">
-        <v>-3.174305691510019</v>
+        <v>-1.72707908432485</v>
       </c>
       <c r="G14">
-        <v>-10.41752044977611</v>
+        <v>-11.10977112646046</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-20.3814275740691</v>
       </c>
       <c r="E15">
-        <v>-25.52571424174029</v>
+        <v>-24.20563263498883</v>
       </c>
       <c r="F15">
-        <v>-3.439763481043746</v>
+        <v>-1.328905239719004</v>
       </c>
       <c r="G15">
-        <v>-9.886074670064502</v>
+        <v>-10.76086991393179</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-19.95576412398018</v>
       </c>
       <c r="E16">
-        <v>-27.62572324996997</v>
+        <v>-24.97561309534409</v>
       </c>
       <c r="F16">
-        <v>-2.900801969392901</v>
+        <v>-1.266407404279989</v>
       </c>
       <c r="G16">
-        <v>-10.95514586193489</v>
+        <v>-10.7910070441193</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-19.53324271090874</v>
       </c>
       <c r="E17">
-        <v>-27.02821734951218</v>
+        <v>-26.34939157131426</v>
       </c>
       <c r="F17">
-        <v>-2.840456232466359</v>
+        <v>-1.003175437957585</v>
       </c>
       <c r="G17">
-        <v>-10.45853133118562</v>
+        <v>-10.21292814452123</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-19.10081784471653</v>
       </c>
       <c r="E18">
-        <v>-27.59603194220877</v>
+        <v>-26.30628539097386</v>
       </c>
       <c r="F18">
-        <v>-2.60695768570004</v>
+        <v>-0.5134819059556429</v>
       </c>
       <c r="G18">
-        <v>-10.82550281240168</v>
+        <v>-9.798877106093615</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-18.68446534925764</v>
       </c>
       <c r="E19">
-        <v>-30.37189925914478</v>
+        <v>-27.06379791093199</v>
       </c>
       <c r="F19">
-        <v>-2.216700548362748</v>
+        <v>-0.5174671815305113</v>
       </c>
       <c r="G19">
-        <v>-9.277593649702911</v>
+        <v>-9.755547883487203</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-18.27150790001592</v>
       </c>
       <c r="E20">
-        <v>-29.75912823046259</v>
+        <v>-27.67693649881643</v>
       </c>
       <c r="F20">
-        <v>-2.051177002302754</v>
+        <v>-0.4384889766128008</v>
       </c>
       <c r="G20">
-        <v>-9.759456168140099</v>
+        <v>-9.392522542720606</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-17.88275372706358</v>
       </c>
       <c r="E21">
-        <v>-31.01481429562258</v>
+        <v>-28.81776135157696</v>
       </c>
       <c r="F21">
-        <v>-2.264952121208417</v>
+        <v>-0.4065322189476016</v>
       </c>
       <c r="G21">
-        <v>-10.16994615094543</v>
+        <v>-9.387406788694319</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-17.51054492175733</v>
       </c>
       <c r="E22">
-        <v>-32.25717893545818</v>
+        <v>-29.02174217258458</v>
       </c>
       <c r="F22">
-        <v>-2.05529481666207</v>
+        <v>-0.1674794687455118</v>
       </c>
       <c r="G22">
-        <v>-9.542479795917266</v>
+        <v>-9.465239611816884</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-17.15766016735153</v>
       </c>
       <c r="E23">
-        <v>-32.15890149587876</v>
+        <v>-29.41371810421058</v>
       </c>
       <c r="F23">
-        <v>-1.680982095093863</v>
+        <v>0.09629590659312917</v>
       </c>
       <c r="G23">
-        <v>-9.244660412058314</v>
+        <v>-9.919069260206992</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-16.83387389298058</v>
       </c>
       <c r="E24">
-        <v>-32.54326459114634</v>
+        <v>-29.15071184385448</v>
       </c>
       <c r="F24">
-        <v>-1.937505113820995</v>
+        <v>-0.2341241114029404</v>
       </c>
       <c r="G24">
-        <v>-9.970426522431078</v>
+        <v>-9.553830008027131</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-16.53011723532541</v>
       </c>
       <c r="E25">
-        <v>-32.83720396944975</v>
+        <v>-29.96757583025007</v>
       </c>
       <c r="F25">
-        <v>-2.331518897329982</v>
+        <v>0.06690791624401111</v>
       </c>
       <c r="G25">
-        <v>-10.08739440697443</v>
+        <v>-9.270676481908758</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-16.27118090921118</v>
       </c>
       <c r="E26">
-        <v>-31.32250703322816</v>
+        <v>-29.8341684526796</v>
       </c>
       <c r="F26">
-        <v>-1.846575224015693</v>
+        <v>-0.1337649154515719</v>
       </c>
       <c r="G26">
-        <v>-9.669671356279418</v>
+        <v>-9.763705154962137</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-16.04847808294213</v>
       </c>
       <c r="E27">
-        <v>-31.935452496786</v>
+        <v>-29.46028183297889</v>
       </c>
       <c r="F27">
-        <v>-2.076638531162602</v>
+        <v>-0.1828175195757474</v>
       </c>
       <c r="G27">
-        <v>-10.28356314480609</v>
+        <v>-9.779082440603794</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-15.89049637195815</v>
       </c>
       <c r="E28">
-        <v>-31.78313139484225</v>
+        <v>-30.01462756134906</v>
       </c>
       <c r="F28">
-        <v>-1.672892259038123</v>
+        <v>0.01610745689992863</v>
       </c>
       <c r="G28">
-        <v>-9.297802118210424</v>
+        <v>-9.734558802346948</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-15.79389541356519</v>
       </c>
       <c r="E29">
-        <v>-30.62833721579066</v>
+        <v>-29.29858900968066</v>
       </c>
       <c r="F29">
-        <v>-2.514919440309793</v>
+        <v>-0.1399470213786646</v>
       </c>
       <c r="G29">
-        <v>-9.282886934361395</v>
+        <v>-9.528295620553747</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-15.7729389122052</v>
       </c>
       <c r="E30">
-        <v>-30.33959973467159</v>
+        <v>-28.72372641736585</v>
       </c>
       <c r="F30">
-        <v>-2.3693694890661</v>
+        <v>0.0002110864402061218</v>
       </c>
       <c r="G30">
-        <v>-9.461219065146569</v>
+        <v>-10.05926885549437</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-15.83151126611236</v>
       </c>
       <c r="E31">
-        <v>-31.57926271054039</v>
+        <v>-29.12090632278185</v>
       </c>
       <c r="F31">
-        <v>-2.892588706594144</v>
+        <v>-0.1654400281998194</v>
       </c>
       <c r="G31">
-        <v>-10.54036773113866</v>
+        <v>-9.800260800726905</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-15.9532546977691</v>
       </c>
       <c r="E32">
-        <v>-31.29865514058967</v>
+        <v>-29.04586194735353</v>
       </c>
       <c r="F32">
-        <v>-1.534145689273623</v>
+        <v>-0.0282400203763457</v>
       </c>
       <c r="G32">
-        <v>-9.643065258151383</v>
+        <v>-10.33491518554099</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-16.14451738372423</v>
       </c>
       <c r="E33">
-        <v>-31.99837987817413</v>
+        <v>-28.19443078310139</v>
       </c>
       <c r="F33">
-        <v>-2.341250557578071</v>
+        <v>-0.1964946937633701</v>
       </c>
       <c r="G33">
-        <v>-10.77795723728062</v>
+        <v>-10.18739767316473</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-16.37383739503236</v>
       </c>
       <c r="E34">
-        <v>-30.29759623193794</v>
+        <v>-27.91160124509189</v>
       </c>
       <c r="F34">
-        <v>-1.948118985353065</v>
+        <v>-0.04599110545093631</v>
       </c>
       <c r="G34">
-        <v>-10.82472350514124</v>
+        <v>-10.03992323807422</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-16.64399371651861</v>
       </c>
       <c r="E35">
-        <v>-29.12169543293357</v>
+        <v>-27.07289759694469</v>
       </c>
       <c r="F35">
-        <v>-1.917786656164755</v>
+        <v>-0.1481785082602833</v>
       </c>
       <c r="G35">
-        <v>-9.569484032595446</v>
+        <v>-10.71047732183412</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-16.92488481748477</v>
       </c>
       <c r="E36">
-        <v>-30.09908103703378</v>
+        <v>-26.69939514929153</v>
       </c>
       <c r="F36">
-        <v>-2.051722896421199</v>
+        <v>0.1289675453269445</v>
       </c>
       <c r="G36">
-        <v>-10.11517795091306</v>
+        <v>-10.14174097175534</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-17.21556344196419</v>
       </c>
       <c r="E37">
-        <v>-28.78794752408167</v>
+        <v>-26.8213666594791</v>
       </c>
       <c r="F37">
-        <v>-1.499430468157101</v>
+        <v>-0.2624203135151688</v>
       </c>
       <c r="G37">
-        <v>-10.67461743950288</v>
+        <v>-10.08812933157683</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-17.50425661962932</v>
       </c>
       <c r="E38">
-        <v>-28.03486025079015</v>
+        <v>-25.66995111784026</v>
       </c>
       <c r="F38">
-        <v>-1.634917412191586</v>
+        <v>0.08155676539511757</v>
       </c>
       <c r="G38">
-        <v>-9.636653269435609</v>
+        <v>-10.639505535497</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-17.77833462201999</v>
       </c>
       <c r="E39">
-        <v>-27.56384870765267</v>
+        <v>-26.13786021211809</v>
       </c>
       <c r="F39">
-        <v>-1.832795332270123</v>
+        <v>-0.06957224030642983</v>
       </c>
       <c r="G39">
-        <v>-10.67192967794633</v>
+        <v>-10.72807765649511</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-18.04633295839956</v>
       </c>
       <c r="E40">
-        <v>-27.52595065431361</v>
+        <v>-24.28616755578858</v>
       </c>
       <c r="F40">
-        <v>-1.276138236160675</v>
+        <v>-0.0699491474747036</v>
       </c>
       <c r="G40">
-        <v>-11.02934452858663</v>
+        <v>-10.63163414055479</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-18.28893965689368</v>
       </c>
       <c r="E41">
-        <v>-27.81087756404215</v>
+        <v>-24.68896260291575</v>
       </c>
       <c r="F41">
-        <v>-1.526207444452595</v>
+        <v>0.1980840363143268</v>
       </c>
       <c r="G41">
-        <v>-10.54528115245913</v>
+        <v>-11.34096822447109</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-18.5237758590416</v>
       </c>
       <c r="E42">
-        <v>-26.65076104467779</v>
+        <v>-24.04626976324384</v>
       </c>
       <c r="F42">
-        <v>-1.94950235891574</v>
+        <v>0.3744558818813836</v>
       </c>
       <c r="G42">
-        <v>-11.58087215569308</v>
+        <v>-11.14305028776338</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-18.73531094359153</v>
       </c>
       <c r="E43">
-        <v>-25.86723696219226</v>
+        <v>-23.12517055562336</v>
       </c>
       <c r="F43">
-        <v>-1.452988049719147</v>
+        <v>0.04610761075971553</v>
       </c>
       <c r="G43">
-        <v>-10.76051093655051</v>
+        <v>-11.1214829266962</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-18.94166543041964</v>
       </c>
       <c r="E44">
-        <v>-26.08183754455748</v>
+        <v>-23.52360473085946</v>
       </c>
       <c r="F44">
-        <v>-1.648288090440172</v>
+        <v>0.1222627395686853</v>
       </c>
       <c r="G44">
-        <v>-10.67078356107083</v>
+        <v>-11.29942083504811</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-19.1402537778288</v>
       </c>
       <c r="E45">
-        <v>-25.7445137207549</v>
+        <v>-22.58754150283563</v>
       </c>
       <c r="F45">
-        <v>-1.792291479742838</v>
+        <v>0.4123901387251842</v>
       </c>
       <c r="G45">
-        <v>-10.88679656853955</v>
+        <v>-11.60077386171114</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-19.33742307398166</v>
       </c>
       <c r="E46">
-        <v>-24.24617213073049</v>
+        <v>-22.21058358336022</v>
       </c>
       <c r="F46">
-        <v>-1.553010928504979</v>
+        <v>0.1318867120544099</v>
       </c>
       <c r="G46">
-        <v>-10.65624301907063</v>
+        <v>-11.04939765779097</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-19.54601835715893</v>
       </c>
       <c r="E47">
-        <v>-24.4541483410326</v>
+        <v>-21.25176491048765</v>
       </c>
       <c r="F47">
-        <v>-1.215225067563216</v>
+        <v>0.3276166754574883</v>
       </c>
       <c r="G47">
-        <v>-11.90941739264485</v>
+        <v>-11.50352884718135</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-19.75337602260087</v>
       </c>
       <c r="E48">
-        <v>-23.62412905776561</v>
+        <v>-20.76182303013161</v>
       </c>
       <c r="F48">
-        <v>-1.973274018273877</v>
+        <v>0.2296854243637252</v>
       </c>
       <c r="G48">
-        <v>-12.05825333103962</v>
+        <v>-11.65291043119567</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-19.98055831148177</v>
       </c>
       <c r="E49">
-        <v>-24.71840887120879</v>
+        <v>-20.21342054716727</v>
       </c>
       <c r="F49">
-        <v>-1.449211522729784</v>
+        <v>0.2594370680026722</v>
       </c>
       <c r="G49">
-        <v>-12.05903524904466</v>
+        <v>-12.24336948164481</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-20.20695395590097</v>
       </c>
       <c r="E50">
-        <v>-23.40749755506256</v>
+        <v>-19.12223902937242</v>
       </c>
       <c r="F50">
-        <v>-1.40225137466508</v>
+        <v>0.09095293684507237</v>
       </c>
       <c r="G50">
-        <v>-11.34836576927001</v>
+        <v>-11.43390942654243</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-20.44852585855244</v>
       </c>
       <c r="E51">
-        <v>-22.53546853924493</v>
+        <v>-18.97022734167237</v>
       </c>
       <c r="F51">
-        <v>-1.29992397776466</v>
+        <v>0.1681012781699987</v>
       </c>
       <c r="G51">
-        <v>-11.35032382771334</v>
+        <v>-11.67924109576934</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-20.68557163544464</v>
       </c>
       <c r="E52">
-        <v>-21.53586948437388</v>
+        <v>-18.89178563938033</v>
       </c>
       <c r="F52">
-        <v>-1.76981538700268</v>
+        <v>0.2070593971236595</v>
       </c>
       <c r="G52">
-        <v>-11.67873461131867</v>
+        <v>-11.84452603046043</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-20.92324272997828</v>
       </c>
       <c r="E53">
-        <v>-21.36743599909545</v>
+        <v>-18.36849762529723</v>
       </c>
       <c r="F53">
-        <v>-1.486238717267519</v>
+        <v>0.0007395848431922063</v>
       </c>
       <c r="G53">
-        <v>-12.6874506097317</v>
+        <v>-11.73183585092962</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-21.15906228633061</v>
       </c>
       <c r="E54">
-        <v>-20.73959504312112</v>
+        <v>-17.18470364817003</v>
       </c>
       <c r="F54">
-        <v>-1.772393266360192</v>
+        <v>0.01795885804518553</v>
       </c>
       <c r="G54">
-        <v>-12.63897952565309</v>
+        <v>-11.92628671882033</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-21.37726124965781</v>
       </c>
       <c r="E55">
-        <v>-22.15119266141517</v>
+        <v>-16.71096759840346</v>
       </c>
       <c r="F55">
-        <v>-1.771212014443799</v>
+        <v>0.1432353454727632</v>
       </c>
       <c r="G55">
-        <v>-12.58552714089464</v>
+        <v>-12.4284529979426</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-21.59329738355843</v>
       </c>
       <c r="E56">
-        <v>-20.30336249161776</v>
+        <v>-18.28867290363403</v>
       </c>
       <c r="F56">
-        <v>-1.766177197369584</v>
+        <v>0.06444103811847419</v>
       </c>
       <c r="G56">
-        <v>-11.49765728259594</v>
+        <v>-11.99280065876812</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-21.7834877052753</v>
       </c>
       <c r="E57">
-        <v>-20.05410336074685</v>
+        <v>-16.55854474278226</v>
       </c>
       <c r="F57">
-        <v>-1.3610682608675</v>
+        <v>-0.04522486560334676</v>
       </c>
       <c r="G57">
-        <v>-11.77471080397717</v>
+        <v>-12.30663304457666</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-21.96623030428639</v>
       </c>
       <c r="E58">
-        <v>-21.03237982867623</v>
+        <v>-16.23380514929391</v>
       </c>
       <c r="F58">
-        <v>-0.9647466457743128</v>
+        <v>0.2536567202659373</v>
       </c>
       <c r="G58">
-        <v>-13.37876794522472</v>
+        <v>-12.0431018748051</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-22.11996462018995</v>
       </c>
       <c r="E59">
-        <v>-20.238618080275</v>
+        <v>-15.98825068292475</v>
       </c>
       <c r="F59">
-        <v>-1.373203843318513</v>
+        <v>0.2976778207855086</v>
       </c>
       <c r="G59">
-        <v>-13.37951200743319</v>
+        <v>-12.53129022738655</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-22.25873848514025</v>
       </c>
       <c r="E60">
-        <v>-20.21052991208519</v>
+        <v>-15.77907004133843</v>
       </c>
       <c r="F60">
-        <v>-1.215261515728939</v>
+        <v>0.2382855347395896</v>
       </c>
       <c r="G60">
-        <v>-12.22230468891141</v>
+        <v>-12.75047659490576</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-22.37559612531824</v>
       </c>
       <c r="E61">
-        <v>-18.69285097013237</v>
+        <v>-15.45191327885904</v>
       </c>
       <c r="F61">
-        <v>-1.715196982299094</v>
+        <v>0.05053771962988728</v>
       </c>
       <c r="G61">
-        <v>-12.10332261491601</v>
+        <v>-12.45343782367956</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-22.46677981312665</v>
       </c>
       <c r="E62">
-        <v>-19.30406246796209</v>
+        <v>-15.69765879294915</v>
       </c>
       <c r="F62">
-        <v>-1.398560169518205</v>
+        <v>0.03735839425134715</v>
       </c>
       <c r="G62">
-        <v>-12.81461345190335</v>
+        <v>-12.38718234744628</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-22.54287944711197</v>
       </c>
       <c r="E63">
-        <v>-19.84790057168043</v>
+        <v>-15.1428312920653</v>
       </c>
       <c r="F63">
-        <v>-1.848499521492396</v>
+        <v>0.05937639981775801</v>
       </c>
       <c r="G63">
-        <v>-12.66646152859144</v>
+        <v>-13.26366413231943</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-22.58398841227137</v>
       </c>
       <c r="E64">
-        <v>-17.17263026284875</v>
+        <v>-15.16781285818414</v>
       </c>
       <c r="F64">
-        <v>-1.807779465072981</v>
+        <v>-0.13841288494868</v>
       </c>
       <c r="G64">
-        <v>-12.93809775494612</v>
+        <v>-12.57337804093989</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-22.6092842170186</v>
       </c>
       <c r="E65">
-        <v>-19.42385769541544</v>
+        <v>-14.08213849860601</v>
       </c>
       <c r="F65">
-        <v>-1.69308040101175</v>
+        <v>0.05714643476942174</v>
       </c>
       <c r="G65">
-        <v>-11.52067491228349</v>
+        <v>-12.85461528052839</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-22.5953158363464</v>
       </c>
       <c r="E66">
-        <v>-19.13702446168881</v>
+        <v>-14.98390450750941</v>
       </c>
       <c r="F66">
-        <v>-2.141576736970264</v>
+        <v>-0.1201813467804656</v>
       </c>
       <c r="G66">
-        <v>-12.84117255662875</v>
+        <v>-12.90146770296051</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-22.55840325179267</v>
       </c>
       <c r="E67">
-        <v>-18.95049543466811</v>
+        <v>-14.31079354809445</v>
       </c>
       <c r="F67">
-        <v>-1.085196236345778</v>
+        <v>-0.2050326765840246</v>
       </c>
       <c r="G67">
-        <v>-13.42339470789292</v>
+        <v>-13.15266310453906</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-22.48206470338479</v>
       </c>
       <c r="E68">
-        <v>-17.53556694089155</v>
+        <v>-15.02194792324484</v>
       </c>
       <c r="F68">
-        <v>-1.618915839071708</v>
+        <v>-0.006795245052672097</v>
       </c>
       <c r="G68">
-        <v>-13.3540689960205</v>
+        <v>-13.15081991885774</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-22.37234975105555</v>
       </c>
       <c r="E69">
-        <v>-17.70214394070777</v>
+        <v>-14.75430667905024</v>
       </c>
       <c r="F69">
-        <v>-1.387590100002932</v>
+        <v>-0.05729832049914955</v>
       </c>
       <c r="G69">
-        <v>-12.49694849303505</v>
+        <v>-13.00077651108957</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-22.23498654301575</v>
       </c>
       <c r="E70">
-        <v>-16.53311047662901</v>
+        <v>-14.24138092722259</v>
       </c>
       <c r="F70">
-        <v>-2.44098847797734</v>
+        <v>-0.2053582249733248</v>
       </c>
       <c r="G70">
-        <v>-12.7686813169396</v>
+        <v>-13.23569783625942</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-22.06013163983961</v>
       </c>
       <c r="E71">
-        <v>-16.25735801071701</v>
+        <v>-14.42734511750311</v>
       </c>
       <c r="F71">
-        <v>-1.285892262328639</v>
+        <v>-0.3006337301737128</v>
       </c>
       <c r="G71">
-        <v>-11.92237973953972</v>
+        <v>-13.01381326420529</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-21.87352537599218</v>
       </c>
       <c r="E72">
-        <v>-17.95723418027874</v>
+        <v>-14.58239280268161</v>
       </c>
       <c r="F72">
-        <v>-2.024081932924585</v>
+        <v>-0.2516697613616368</v>
       </c>
       <c r="G72">
-        <v>-12.84841737286908</v>
+        <v>-13.33143122967095</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-21.66182671376984</v>
       </c>
       <c r="E73">
-        <v>-19.47176914125866</v>
+        <v>-15.02835217510773</v>
       </c>
       <c r="F73">
-        <v>-2.116987478985564</v>
+        <v>-0.09560948451122389</v>
       </c>
       <c r="G73">
-        <v>-13.26922632367079</v>
+        <v>-12.61072343694347</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-21.45414095197591</v>
       </c>
       <c r="E74">
-        <v>-19.07837281135958</v>
+        <v>-15.49941355678111</v>
       </c>
       <c r="F74">
-        <v>-2.019361895463433</v>
+        <v>-0.1703729560834905</v>
       </c>
       <c r="G74">
-        <v>-12.33027986371067</v>
+        <v>-12.5505496902352</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-21.23704340762356</v>
       </c>
       <c r="E75">
-        <v>-18.13907423171371</v>
+        <v>-15.93385192099214</v>
       </c>
       <c r="F75">
-        <v>-1.36461615845369</v>
+        <v>-0.1414281422948701</v>
       </c>
       <c r="G75">
-        <v>-12.95118411220908</v>
+        <v>-12.30384738009795</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-21.02957903340738</v>
       </c>
       <c r="E76">
-        <v>-18.45076028200811</v>
+        <v>-14.92747897845029</v>
       </c>
       <c r="F76">
-        <v>-2.306596635649356</v>
+        <v>-0.09973723927937382</v>
       </c>
       <c r="G76">
-        <v>-13.73249120301318</v>
+        <v>-12.18845769065992</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-20.82941850019626</v>
       </c>
       <c r="E77">
-        <v>-19.31487327704061</v>
+        <v>-15.56530425444951</v>
       </c>
       <c r="F77">
-        <v>-2.002066412460382</v>
+        <v>-0.1865219786010668</v>
       </c>
       <c r="G77">
-        <v>-12.50748284746019</v>
+        <v>-12.24661333179927</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-20.63026583269927</v>
       </c>
       <c r="E78">
-        <v>-19.97734370904137</v>
+        <v>-16.21774883431213</v>
       </c>
       <c r="F78">
-        <v>-1.955885758121713</v>
+        <v>-0.328306171631633</v>
       </c>
       <c r="G78">
-        <v>-11.87145063942858</v>
+        <v>-11.78706876349921</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-20.44426564094893</v>
       </c>
       <c r="E79">
-        <v>-21.72965417157905</v>
+        <v>-16.98559454404642</v>
       </c>
       <c r="F79">
-        <v>-2.347992639869456</v>
+        <v>-0.6080864335597632</v>
       </c>
       <c r="G79">
-        <v>-11.77289764185865</v>
+        <v>-11.6618913925891</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-20.2507596083329</v>
       </c>
       <c r="E80">
-        <v>-20.76875473983274</v>
+        <v>-16.72762197581602</v>
       </c>
       <c r="F80">
-        <v>-2.56520051329232</v>
+        <v>-0.5512877658520096</v>
       </c>
       <c r="G80">
-        <v>-11.33439828570755</v>
+        <v>-11.56201996900065</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-20.06636666939153</v>
       </c>
       <c r="E81">
-        <v>-21.06263597317761</v>
+        <v>-17.22628144674289</v>
       </c>
       <c r="F81">
-        <v>-2.007280985261005</v>
+        <v>-0.3032762221886431</v>
       </c>
       <c r="G81">
-        <v>-12.03536884932622</v>
+        <v>-11.20027128233911</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-19.86728601398503</v>
       </c>
       <c r="E82">
-        <v>-21.25527022084581</v>
+        <v>-16.98875513786462</v>
       </c>
       <c r="F82">
-        <v>-2.225545855489842</v>
+        <v>-0.6310255836780871</v>
       </c>
       <c r="G82">
-        <v>-11.68513746242837</v>
+        <v>-11.00809437298726</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-19.6682269588471</v>
       </c>
       <c r="E83">
-        <v>-20.34878616387741</v>
+        <v>-18.86916309729399</v>
       </c>
       <c r="F83">
-        <v>-2.357931391968244</v>
+        <v>-0.4434550391925839</v>
       </c>
       <c r="G83">
-        <v>-11.99261790664674</v>
+        <v>-10.77939445217803</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-19.45868713180285</v>
       </c>
       <c r="E84">
-        <v>-22.3078351797424</v>
+        <v>-19.45868237237413</v>
       </c>
       <c r="F84">
-        <v>-2.185930841185761</v>
+        <v>-0.5849890652675046</v>
       </c>
       <c r="G84">
-        <v>-11.74143555879114</v>
+        <v>-11.14567147533286</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-19.24308279227393</v>
       </c>
       <c r="E85">
-        <v>-23.43287367625726</v>
+        <v>-20.76981380872057</v>
       </c>
       <c r="F85">
-        <v>-2.435266944326203</v>
+        <v>-0.5670698216101457</v>
       </c>
       <c r="G85">
-        <v>-11.33234362971435</v>
+        <v>-10.36789541658823</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-19.03263767057229</v>
       </c>
       <c r="E86">
-        <v>-23.92404490716546</v>
+        <v>-21.65443951448641</v>
       </c>
       <c r="F86">
-        <v>-2.573784056320128</v>
+        <v>-0.659439413961513</v>
       </c>
       <c r="G86">
-        <v>-11.33271827156317</v>
+        <v>-10.1654021499846</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-18.81817992873852</v>
       </c>
       <c r="E87">
-        <v>-24.22966311571429</v>
+        <v>-22.00583026504617</v>
       </c>
       <c r="F87">
-        <v>-2.397088319098577</v>
+        <v>-1.182344680243895</v>
       </c>
       <c r="G87">
-        <v>-11.31335176818629</v>
+        <v>-10.30049251810717</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-18.62519527308696</v>
       </c>
       <c r="E88">
-        <v>-27.81441194687958</v>
+        <v>-22.68100121727825</v>
       </c>
       <c r="F88">
-        <v>-2.785364829975776</v>
+        <v>-0.9083008625801516</v>
       </c>
       <c r="G88">
-        <v>-10.32510922885677</v>
+        <v>-10.43963606720744</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-18.44267551009544</v>
       </c>
       <c r="E89">
-        <v>-27.09447352977717</v>
+        <v>-23.6682029363447</v>
       </c>
       <c r="F89">
-        <v>-1.82382577003261</v>
+        <v>-1.160563587754685</v>
       </c>
       <c r="G89">
-        <v>-10.34486081706084</v>
+        <v>-9.734550970113174</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-18.29838192620831</v>
       </c>
       <c r="E90">
-        <v>-27.87313835501265</v>
+        <v>-25.36674177185983</v>
       </c>
       <c r="F90">
-        <v>-2.096692477616976</v>
+        <v>-1.214475395063683</v>
       </c>
       <c r="G90">
-        <v>-11.46451779612864</v>
+        <v>-9.897578916105244</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-18.18541857767736</v>
       </c>
       <c r="E91">
-        <v>-29.96431763596575</v>
+        <v>-26.35215761005659</v>
       </c>
       <c r="F91">
-        <v>-2.732572975395363</v>
+        <v>-1.526841145515737</v>
       </c>
       <c r="G91">
-        <v>-11.51770649568339</v>
+        <v>-10.04622296477257</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-18.12136596201429</v>
       </c>
       <c r="E92">
-        <v>-30.73482555415926</v>
+        <v>-28.52011938537746</v>
       </c>
       <c r="F92">
-        <v>-3.461040926152054</v>
+        <v>-1.563126122860564</v>
       </c>
       <c r="G92">
-        <v>-10.39186857879613</v>
+        <v>-9.763985810005682</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-18.1145558193922</v>
       </c>
       <c r="E93">
-        <v>-31.79250519280238</v>
+        <v>-30.11891885092682</v>
       </c>
       <c r="F93">
-        <v>-2.642165785421227</v>
+        <v>-1.427892659251336</v>
       </c>
       <c r="G93">
-        <v>-11.08785262024577</v>
+        <v>-10.03407125407324</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-18.15709437157111</v>
       </c>
       <c r="E94">
-        <v>-34.12586445592322</v>
+        <v>-31.80977632209668</v>
       </c>
       <c r="F94">
-        <v>-2.803792691218453</v>
+        <v>-1.564048095779879</v>
       </c>
       <c r="G94">
-        <v>-10.97619890631763</v>
+        <v>-10.4044523677253</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-18.26535255303399</v>
       </c>
       <c r="E95">
-        <v>-35.31248884656829</v>
+        <v>-33.37443639055596</v>
       </c>
       <c r="F95">
-        <v>-3.008773033408594</v>
+        <v>-1.713457410753215</v>
       </c>
       <c r="G95">
-        <v>-11.67384599207181</v>
+        <v>-10.34555919123896</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-18.41323046595494</v>
       </c>
       <c r="E96">
-        <v>-37.87135917820466</v>
+        <v>-35.25924467738399</v>
       </c>
       <c r="F96">
-        <v>-3.445920735948754</v>
+        <v>-1.690485954306182</v>
       </c>
       <c r="G96">
-        <v>-11.5184100913507</v>
+        <v>-10.5967310961162</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-18.60607732177944</v>
       </c>
       <c r="E97">
-        <v>-41.80927425777109</v>
+        <v>-37.37511687626886</v>
       </c>
       <c r="F97">
-        <v>-2.977336490472352</v>
+        <v>-2.118389904998503</v>
       </c>
       <c r="G97">
-        <v>-11.37457764496479</v>
+        <v>-11.01089961805041</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.80695344953728</v>
       </c>
       <c r="E98">
-        <v>-42.33306481042449</v>
+        <v>-39.18632195199827</v>
       </c>
       <c r="F98">
-        <v>-3.877652572409412</v>
+        <v>-2.000809779110336</v>
       </c>
       <c r="G98">
-        <v>-11.11657211612031</v>
+        <v>-10.8355463468437</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-19.00609640572444</v>
       </c>
       <c r="E99">
-        <v>-43.44631233998815</v>
+        <v>-41.45658770527797</v>
       </c>
       <c r="F99">
-        <v>-3.81380615483864</v>
+        <v>-2.397241567068095</v>
       </c>
       <c r="G99">
-        <v>-11.46074788093907</v>
+        <v>-11.30294142412923</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-19.17449927257239</v>
       </c>
       <c r="E100">
-        <v>-44.55454071366577</v>
+        <v>-44.14607030326322</v>
       </c>
       <c r="F100">
-        <v>-3.651359993680046</v>
+        <v>-2.356953090065538</v>
       </c>
       <c r="G100">
-        <v>-11.1237451368844</v>
+        <v>-11.11011966086338</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-19.28552237913768</v>
       </c>
       <c r="E101">
-        <v>-46.90942295617469</v>
+        <v>-45.59962262405785</v>
       </c>
       <c r="F101">
-        <v>-4.088375985803161</v>
+        <v>-2.493306506403351</v>
       </c>
       <c r="G101">
-        <v>-11.89749281672494</v>
+        <v>-11.33310727250725</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-19.33304972760036</v>
       </c>
       <c r="E102">
-        <v>-49.29975285734103</v>
+        <v>-48.2293135152052</v>
       </c>
       <c r="F102">
-        <v>-3.943547542567307</v>
+        <v>-2.761785351855087</v>
       </c>
       <c r="G102">
-        <v>-11.99897768047069</v>
+        <v>-12.26710245535032</v>
       </c>
     </row>
   </sheetData>
